--- a/static/data/exports/Retro_MN_AE_2022.xlsx
+++ b/static/data/exports/Retro_MN_AE_2022.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -576,6 +576,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>55</v>
+      </c>
       <c r="Q2" t="b">
         <v>1</v>
       </c>
@@ -638,8 +651,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>64</v>
+      </c>
       <c r="Q3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>45</v>
@@ -700,6 +726,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>45</v>
+      </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
@@ -763,7 +802,7 @@
         </is>
       </c>
       <c r="Q5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>45</v>
@@ -824,6 +863,19 @@
           <t>SHS</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>60</v>
+      </c>
       <c r="Q6" t="b">
         <v>0</v>
       </c>
@@ -886,6 +938,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>61</v>
+      </c>
       <c r="Q7" t="b">
         <v>1</v>
       </c>
@@ -948,6 +1013,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>57</v>
+      </c>
       <c r="Q8" t="b">
         <v>0</v>
       </c>
@@ -1011,7 +1089,7 @@
         </is>
       </c>
       <c r="Q9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>45</v>
@@ -1072,6 +1150,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>38</v>
+      </c>
       <c r="Q10" t="b">
         <v>1</v>
       </c>
@@ -1134,6 +1225,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>31</v>
+      </c>
       <c r="Q11" t="b">
         <v>0</v>
       </c>
@@ -1196,6 +1300,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>64</v>
+      </c>
       <c r="Q12" t="b">
         <v>0</v>
       </c>
@@ -1258,6 +1375,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>33</v>
+      </c>
       <c r="Q13" t="b">
         <v>0</v>
       </c>
@@ -1320,6 +1450,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>67</v>
+      </c>
       <c r="Q14" t="b">
         <v>0</v>
       </c>
@@ -1382,6 +1525,19 @@
           <t>LJPRV</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>56</v>
+      </c>
       <c r="Q15" t="b">
         <v>0</v>
       </c>
@@ -1444,6 +1600,19 @@
           <t>CPI</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>57</v>
+      </c>
       <c r="Q16" t="b">
         <v>0</v>
       </c>
@@ -1507,7 +1676,7 @@
         </is>
       </c>
       <c r="Q17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>45</v>
@@ -1568,6 +1737,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>36</v>
+      </c>
       <c r="Q18" t="b">
         <v>0</v>
       </c>
@@ -1630,6 +1812,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>45</v>
+      </c>
       <c r="Q19" t="b">
         <v>1</v>
       </c>
@@ -1692,6 +1887,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>41</v>
+      </c>
       <c r="Q20" t="b">
         <v>0</v>
       </c>
@@ -1754,6 +1962,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>42</v>
+      </c>
       <c r="Q21" t="b">
         <v>0</v>
       </c>
@@ -1817,7 +2038,7 @@
         </is>
       </c>
       <c r="Q22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>45</v>
@@ -1878,6 +2099,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>53</v>
+      </c>
       <c r="Q23" t="b">
         <v>0</v>
       </c>
@@ -1940,6 +2174,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>46</v>
+      </c>
       <c r="Q24" t="b">
         <v>1</v>
       </c>
@@ -2002,6 +2249,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>47</v>
+      </c>
       <c r="Q25" t="b">
         <v>0</v>
       </c>
@@ -2064,6 +2324,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>37</v>
+      </c>
       <c r="Q26" t="b">
         <v>0</v>
       </c>
@@ -2127,7 +2400,7 @@
         </is>
       </c>
       <c r="Q27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>45</v>
@@ -2188,6 +2461,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>42</v>
+      </c>
       <c r="Q28" t="b">
         <v>1</v>
       </c>
@@ -2250,6 +2536,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>40</v>
+      </c>
       <c r="Q29" t="b">
         <v>0</v>
       </c>
@@ -2312,6 +2611,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>58</v>
+      </c>
       <c r="Q30" t="b">
         <v>0</v>
       </c>
@@ -2374,6 +2686,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>49</v>
+      </c>
       <c r="Q31" t="b">
         <v>0</v>
       </c>
@@ -2436,6 +2761,19 @@
           <t>SHS</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>59</v>
+      </c>
       <c r="Q32" t="b">
         <v>0</v>
       </c>
@@ -2498,6 +2836,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>44</v>
+      </c>
       <c r="Q33" t="b">
         <v>0</v>
       </c>
@@ -2561,7 +2912,7 @@
         </is>
       </c>
       <c r="Q34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>45</v>
@@ -2622,6 +2973,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>51</v>
+      </c>
       <c r="Q35" t="b">
         <v>0</v>
       </c>
@@ -2684,6 +3048,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>40</v>
+      </c>
       <c r="Q36" t="b">
         <v>0</v>
       </c>
@@ -2746,6 +3123,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>37</v>
+      </c>
       <c r="Q37" t="b">
         <v>0</v>
       </c>
@@ -2808,6 +3198,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>59</v>
+      </c>
       <c r="Q38" t="b">
         <v>0</v>
       </c>
@@ -2871,7 +3274,7 @@
         </is>
       </c>
       <c r="Q39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>45</v>
@@ -2932,8 +3335,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>63</v>
+      </c>
       <c r="Q40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>45</v>
@@ -2994,6 +3410,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>60</v>
+      </c>
       <c r="Q41" t="b">
         <v>0</v>
       </c>
@@ -3056,6 +3485,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>41</v>
+      </c>
       <c r="Q42" t="b">
         <v>0</v>
       </c>
@@ -3118,6 +3560,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>35</v>
+      </c>
       <c r="Q43" t="b">
         <v>0</v>
       </c>
@@ -3180,6 +3635,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>40</v>
+      </c>
       <c r="Q44" t="b">
         <v>0</v>
       </c>
@@ -3243,7 +3711,7 @@
         </is>
       </c>
       <c r="Q45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>45</v>
@@ -3304,6 +3772,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>57</v>
+      </c>
       <c r="Q46" t="b">
         <v>0</v>
       </c>
@@ -3366,6 +3847,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>57</v>
+      </c>
       <c r="Q47" t="b">
         <v>0</v>
       </c>
@@ -3428,6 +3922,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>55</v>
+      </c>
       <c r="Q48" t="b">
         <v>0</v>
       </c>
@@ -3491,7 +3998,7 @@
         </is>
       </c>
       <c r="Q49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
         <v>45</v>
@@ -3552,6 +4059,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>59</v>
+      </c>
       <c r="Q50" t="b">
         <v>0</v>
       </c>
@@ -3614,6 +4134,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>68</v>
+      </c>
       <c r="Q51" t="b">
         <v>1</v>
       </c>
@@ -3676,6 +4209,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>43</v>
+      </c>
       <c r="Q52" t="b">
         <v>0</v>
       </c>
@@ -3738,6 +4284,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>38</v>
+      </c>
       <c r="Q53" t="b">
         <v>0</v>
       </c>
@@ -3801,7 +4360,7 @@
         </is>
       </c>
       <c r="Q54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
         <v>45</v>
@@ -3862,6 +4421,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>45</v>
+      </c>
       <c r="Q55" t="b">
         <v>0</v>
       </c>
@@ -3924,6 +4496,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>59</v>
+      </c>
       <c r="Q56" t="b">
         <v>0</v>
       </c>
@@ -3986,6 +4571,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>47</v>
+      </c>
       <c r="Q57" t="b">
         <v>0</v>
       </c>
@@ -4049,7 +4647,7 @@
         </is>
       </c>
       <c r="Q58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
         <v>45</v>
@@ -4110,6 +4708,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>57</v>
+      </c>
       <c r="Q59" t="b">
         <v>0</v>
       </c>
@@ -4172,6 +4783,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>29</v>
+      </c>
       <c r="Q60" t="b">
         <v>0</v>
       </c>
@@ -4234,6 +4858,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>59</v>
+      </c>
       <c r="Q61" t="b">
         <v>0</v>
       </c>
@@ -4296,6 +4933,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>47</v>
+      </c>
       <c r="Q62" t="b">
         <v>0</v>
       </c>
@@ -4359,7 +5009,7 @@
         </is>
       </c>
       <c r="Q63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
         <v>45</v>
@@ -4420,6 +5070,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>77</v>
+      </c>
       <c r="Q64" t="b">
         <v>0</v>
       </c>
@@ -4482,6 +5145,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>58</v>
+      </c>
       <c r="Q65" t="b">
         <v>1</v>
       </c>
@@ -4544,6 +5220,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>51</v>
+      </c>
       <c r="Q66" t="b">
         <v>0</v>
       </c>
@@ -4606,6 +5295,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>47</v>
+      </c>
       <c r="Q67" t="b">
         <v>0</v>
       </c>
@@ -4668,8 +5370,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>57</v>
+      </c>
       <c r="Q68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
         <v>45</v>
@@ -4731,7 +5446,7 @@
         </is>
       </c>
       <c r="Q69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
         <v>45</v>
@@ -4792,6 +5507,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>47</v>
+      </c>
       <c r="Q70" t="b">
         <v>1</v>
       </c>
@@ -4854,6 +5582,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>57</v>
+      </c>
       <c r="Q71" t="b">
         <v>0</v>
       </c>
@@ -4916,6 +5657,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>43</v>
+      </c>
       <c r="Q72" t="b">
         <v>0</v>
       </c>
@@ -4978,6 +5732,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>48</v>
+      </c>
       <c r="Q73" t="b">
         <v>0</v>
       </c>
@@ -5040,6 +5807,19 @@
           <t>SHS</t>
         </is>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>49</v>
+      </c>
       <c r="Q74" t="b">
         <v>0</v>
       </c>
@@ -5103,7 +5883,7 @@
         </is>
       </c>
       <c r="Q75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
         <v>45</v>
@@ -5164,6 +5944,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>54</v>
+      </c>
       <c r="Q76" t="b">
         <v>0</v>
       </c>
@@ -5226,6 +6019,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>37</v>
+      </c>
       <c r="Q77" t="b">
         <v>0</v>
       </c>
@@ -5288,6 +6094,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>82</v>
+      </c>
       <c r="Q78" t="b">
         <v>0</v>
       </c>
@@ -5350,6 +6169,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>47</v>
+      </c>
       <c r="Q79" t="b">
         <v>0</v>
       </c>
@@ -5413,7 +6245,7 @@
         </is>
       </c>
       <c r="Q80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
         <v>45</v>
@@ -5474,6 +6306,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>43</v>
+      </c>
       <c r="Q81" t="b">
         <v>1</v>
       </c>
@@ -5536,6 +6381,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>51</v>
+      </c>
       <c r="Q82" t="b">
         <v>0</v>
       </c>
@@ -5598,6 +6456,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>58</v>
+      </c>
       <c r="Q83" t="b">
         <v>0</v>
       </c>
@@ -5660,6 +6531,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>26</v>
+      </c>
       <c r="Q84" t="b">
         <v>0</v>
       </c>
@@ -5722,6 +6606,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>59</v>
+      </c>
       <c r="Q85" t="b">
         <v>0</v>
       </c>
@@ -5784,6 +6681,19 @@
           <t>SHS</t>
         </is>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>48</v>
+      </c>
       <c r="Q86" t="b">
         <v>0</v>
       </c>
@@ -5847,7 +6757,7 @@
         </is>
       </c>
       <c r="Q87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
         <v>45</v>
@@ -5908,6 +6818,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>35</v>
+      </c>
       <c r="Q88" t="b">
         <v>0</v>
       </c>
@@ -5970,6 +6893,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>49</v>
+      </c>
       <c r="Q89" t="b">
         <v>0</v>
       </c>
@@ -6032,6 +6968,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>56</v>
+      </c>
       <c r="Q90" t="b">
         <v>1</v>
       </c>
@@ -6094,6 +7043,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>63</v>
+      </c>
       <c r="Q91" t="b">
         <v>0</v>
       </c>
@@ -6156,6 +7118,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>43</v>
+      </c>
       <c r="Q92" t="b">
         <v>0</v>
       </c>
@@ -6218,6 +7193,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>46</v>
+      </c>
       <c r="Q93" t="b">
         <v>0</v>
       </c>
@@ -6280,6 +7268,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>60</v>
+      </c>
       <c r="Q94" t="b">
         <v>0</v>
       </c>
@@ -6343,7 +7344,7 @@
         </is>
       </c>
       <c r="Q95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
         <v>45</v>
@@ -6404,6 +7405,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>49</v>
+      </c>
       <c r="Q96" t="b">
         <v>1</v>
       </c>
@@ -6466,6 +7480,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>58</v>
+      </c>
       <c r="Q97" t="b">
         <v>0</v>
       </c>
@@ -6528,6 +7555,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>40</v>
+      </c>
       <c r="Q98" t="b">
         <v>0</v>
       </c>
@@ -6590,6 +7630,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>43</v>
+      </c>
       <c r="Q99" t="b">
         <v>0</v>
       </c>
@@ -6653,7 +7706,7 @@
         </is>
       </c>
       <c r="Q100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
         <v>45</v>
@@ -6714,6 +7767,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>44</v>
+      </c>
       <c r="Q101" t="b">
         <v>0</v>
       </c>
@@ -6776,6 +7842,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>63</v>
+      </c>
       <c r="Q102" t="b">
         <v>0</v>
       </c>
@@ -6838,6 +7917,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>57</v>
+      </c>
       <c r="Q103" t="b">
         <v>0</v>
       </c>
@@ -6900,6 +7992,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>52</v>
+      </c>
       <c r="Q104" t="b">
         <v>0</v>
       </c>
@@ -6963,7 +8068,7 @@
         </is>
       </c>
       <c r="Q105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
         <v>45</v>
@@ -7024,6 +8129,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>54</v>
+      </c>
       <c r="Q106" t="b">
         <v>0</v>
       </c>
@@ -7086,6 +8204,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>59</v>
+      </c>
       <c r="Q107" t="b">
         <v>0</v>
       </c>
@@ -7148,6 +8279,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>80</v>
+      </c>
       <c r="Q108" t="b">
         <v>0</v>
       </c>
@@ -7210,6 +8354,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>59</v>
+      </c>
       <c r="Q109" t="b">
         <v>0</v>
       </c>
@@ -7272,6 +8429,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>57</v>
+      </c>
       <c r="Q110" t="b">
         <v>0</v>
       </c>
@@ -7335,7 +8505,7 @@
         </is>
       </c>
       <c r="Q111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
         <v>45</v>
@@ -7396,6 +8566,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>32</v>
+      </c>
       <c r="Q112" t="b">
         <v>0</v>
       </c>
@@ -7458,6 +8641,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>55</v>
+      </c>
       <c r="Q113" t="b">
         <v>0</v>
       </c>
@@ -7520,6 +8716,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>53</v>
+      </c>
       <c r="Q114" t="b">
         <v>0</v>
       </c>
@@ -7582,6 +8791,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P115" t="n">
+        <v>66</v>
+      </c>
       <c r="Q115" t="b">
         <v>0</v>
       </c>
@@ -7645,7 +8867,7 @@
         </is>
       </c>
       <c r="Q116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
         <v>45</v>
@@ -7706,8 +8928,21 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>51</v>
+      </c>
       <c r="Q117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
         <v>45</v>
@@ -7768,6 +9003,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>46</v>
+      </c>
       <c r="Q118" t="b">
         <v>0</v>
       </c>
@@ -7830,6 +9078,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>48</v>
+      </c>
       <c r="Q119" t="b">
         <v>0</v>
       </c>
@@ -7893,7 +9154,7 @@
         </is>
       </c>
       <c r="Q120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
         <v>45</v>
@@ -7954,6 +9215,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P121" t="n">
+        <v>33</v>
+      </c>
       <c r="Q121" t="b">
         <v>1</v>
       </c>
@@ -8016,8 +9290,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P122" t="n">
+        <v>58</v>
+      </c>
       <c r="Q122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
         <v>45</v>
@@ -8078,6 +9365,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>47</v>
+      </c>
       <c r="Q123" t="b">
         <v>0</v>
       </c>
@@ -8141,7 +9441,7 @@
         </is>
       </c>
       <c r="Q124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
         <v>45</v>
@@ -8202,6 +9502,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>57</v>
+      </c>
       <c r="Q125" t="b">
         <v>0</v>
       </c>
@@ -8264,6 +9577,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>53</v>
+      </c>
       <c r="Q126" t="b">
         <v>1</v>
       </c>
@@ -8327,7 +9653,7 @@
         </is>
       </c>
       <c r="Q127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
         <v>45</v>
@@ -8388,6 +9714,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>61</v>
+      </c>
       <c r="Q128" t="b">
         <v>0</v>
       </c>
@@ -8450,6 +9789,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>65</v>
+      </c>
       <c r="Q129" t="b">
         <v>1</v>
       </c>
@@ -8512,6 +9864,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>41</v>
+      </c>
       <c r="Q130" t="b">
         <v>0</v>
       </c>
@@ -8574,6 +9939,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>52</v>
+      </c>
       <c r="Q131" t="b">
         <v>0</v>
       </c>
@@ -8636,6 +10014,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>49</v>
+      </c>
       <c r="Q132" t="b">
         <v>0</v>
       </c>
@@ -8698,6 +10089,19 @@
           <t>SHS</t>
         </is>
       </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
+        <v>49</v>
+      </c>
       <c r="Q133" t="b">
         <v>0</v>
       </c>
@@ -8760,6 +10164,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>27</v>
+      </c>
       <c r="Q134" t="b">
         <v>0</v>
       </c>
@@ -8823,7 +10240,7 @@
         </is>
       </c>
       <c r="Q135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
         <v>45</v>
@@ -8884,6 +10301,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>56</v>
+      </c>
       <c r="Q136" t="b">
         <v>0</v>
       </c>
@@ -8946,6 +10376,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>62</v>
+      </c>
       <c r="Q137" t="b">
         <v>0</v>
       </c>
@@ -9008,6 +10451,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P138" t="n">
+        <v>65</v>
+      </c>
       <c r="Q138" t="b">
         <v>0</v>
       </c>
@@ -9071,7 +10527,7 @@
         </is>
       </c>
       <c r="Q139" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
         <v>45</v>
@@ -9132,6 +10588,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>61</v>
+      </c>
       <c r="Q140" t="b">
         <v>0</v>
       </c>
@@ -9194,6 +10663,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P141" t="n">
+        <v>41</v>
+      </c>
       <c r="Q141" t="b">
         <v>0</v>
       </c>
@@ -9256,6 +10738,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>71</v>
+      </c>
       <c r="Q142" t="b">
         <v>0</v>
       </c>
@@ -9319,7 +10814,7 @@
         </is>
       </c>
       <c r="Q143" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
         <v>45</v>
@@ -9380,6 +10875,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>49</v>
+      </c>
       <c r="Q144" t="b">
         <v>0</v>
       </c>
@@ -9442,6 +10950,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>44</v>
+      </c>
       <c r="Q145" t="b">
         <v>0</v>
       </c>
@@ -9505,7 +11026,7 @@
         </is>
       </c>
       <c r="Q146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R146" t="n">
         <v>45</v>
@@ -9566,6 +11087,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>46</v>
+      </c>
       <c r="Q147" t="b">
         <v>0</v>
       </c>
@@ -9628,6 +11162,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>46</v>
+      </c>
       <c r="Q148" t="b">
         <v>0</v>
       </c>
@@ -9690,6 +11237,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P149" t="n">
+        <v>71</v>
+      </c>
       <c r="Q149" t="b">
         <v>0</v>
       </c>
@@ -9752,6 +11312,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>45</v>
+      </c>
       <c r="Q150" t="b">
         <v>0</v>
       </c>
@@ -9814,6 +11387,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>43</v>
+      </c>
       <c r="Q151" t="b">
         <v>0</v>
       </c>
@@ -9877,7 +11463,7 @@
         </is>
       </c>
       <c r="Q152" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R152" t="n">
         <v>45</v>
@@ -9938,6 +11524,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P153" t="n">
+        <v>48</v>
+      </c>
       <c r="Q153" t="b">
         <v>0</v>
       </c>
@@ -10000,6 +11599,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P154" t="n">
+        <v>34</v>
+      </c>
       <c r="Q154" t="b">
         <v>0</v>
       </c>
@@ -10062,6 +11674,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P155" t="n">
+        <v>52</v>
+      </c>
       <c r="Q155" t="b">
         <v>0</v>
       </c>
@@ -10124,6 +11749,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P156" t="n">
+        <v>41</v>
+      </c>
       <c r="Q156" t="b">
         <v>0</v>
       </c>
@@ -10187,7 +11825,7 @@
         </is>
       </c>
       <c r="Q157" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R157" t="n">
         <v>45</v>
@@ -10248,6 +11886,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P158" t="n">
+        <v>28</v>
+      </c>
       <c r="Q158" t="b">
         <v>0</v>
       </c>
@@ -10310,6 +11961,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P159" t="n">
+        <v>73</v>
+      </c>
       <c r="Q159" t="b">
         <v>1</v>
       </c>
@@ -10372,8 +12036,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P160" t="n">
+        <v>53</v>
+      </c>
       <c r="Q160" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R160" t="n">
         <v>45</v>
@@ -10434,6 +12111,19 @@
           <t>SHS</t>
         </is>
       </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P161" t="n">
+        <v>67</v>
+      </c>
       <c r="Q161" t="b">
         <v>0</v>
       </c>
@@ -10497,7 +12187,7 @@
         </is>
       </c>
       <c r="Q162" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R162" t="n">
         <v>45</v>
@@ -10558,6 +12248,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P163" t="n">
+        <v>62</v>
+      </c>
       <c r="Q163" t="b">
         <v>0</v>
       </c>
@@ -10620,6 +12323,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P164" t="n">
+        <v>48</v>
+      </c>
       <c r="Q164" t="b">
         <v>1</v>
       </c>
@@ -10682,6 +12398,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P165" t="n">
+        <v>47</v>
+      </c>
       <c r="Q165" t="b">
         <v>0</v>
       </c>
@@ -10744,6 +12473,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P166" t="n">
+        <v>74</v>
+      </c>
       <c r="Q166" t="b">
         <v>0</v>
       </c>
@@ -10806,6 +12548,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P167" t="n">
+        <v>48</v>
+      </c>
       <c r="Q167" t="b">
         <v>0</v>
       </c>
@@ -10868,6 +12623,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P168" t="n">
+        <v>52</v>
+      </c>
       <c r="Q168" t="b">
         <v>0</v>
       </c>
@@ -10931,7 +12699,7 @@
         </is>
       </c>
       <c r="Q169" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R169" t="n">
         <v>45</v>
@@ -10992,6 +12760,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P170" t="n">
+        <v>58</v>
+      </c>
       <c r="Q170" t="b">
         <v>0</v>
       </c>
@@ -11054,6 +12835,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P171" t="n">
+        <v>51</v>
+      </c>
       <c r="Q171" t="b">
         <v>0</v>
       </c>
@@ -11116,6 +12910,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P172" t="n">
+        <v>37</v>
+      </c>
       <c r="Q172" t="b">
         <v>0</v>
       </c>
@@ -11178,6 +12985,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P173" t="n">
+        <v>57</v>
+      </c>
       <c r="Q173" t="b">
         <v>1</v>
       </c>
@@ -11240,8 +13060,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P174" t="n">
+        <v>54</v>
+      </c>
       <c r="Q174" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R174" t="n">
         <v>45</v>
@@ -11302,6 +13135,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P175" t="n">
+        <v>53</v>
+      </c>
       <c r="Q175" t="b">
         <v>0</v>
       </c>
@@ -11365,7 +13211,7 @@
         </is>
       </c>
       <c r="Q176" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R176" t="n">
         <v>45</v>
@@ -11426,6 +13272,19 @@
           <t>RJSNP</t>
         </is>
       </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P177" t="n">
+        <v>50</v>
+      </c>
       <c r="Q177" t="b">
         <v>0</v>
       </c>
@@ -11488,6 +13347,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P178" t="n">
+        <v>56</v>
+      </c>
       <c r="Q178" t="b">
         <v>0</v>
       </c>
@@ -11550,6 +13422,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P179" t="n">
+        <v>60</v>
+      </c>
       <c r="Q179" t="b">
         <v>0</v>
       </c>
@@ -11612,6 +13497,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P180" t="n">
+        <v>26</v>
+      </c>
       <c r="Q180" t="b">
         <v>0</v>
       </c>
@@ -11675,7 +13573,7 @@
         </is>
       </c>
       <c r="Q181" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R181" t="n">
         <v>45</v>
@@ -11736,6 +13634,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P182" t="n">
+        <v>34</v>
+      </c>
       <c r="Q182" t="b">
         <v>1</v>
       </c>
@@ -11798,6 +13709,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P183" t="n">
+        <v>57</v>
+      </c>
       <c r="Q183" t="b">
         <v>0</v>
       </c>
@@ -11860,6 +13784,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P184" t="n">
+        <v>57</v>
+      </c>
       <c r="Q184" t="b">
         <v>0</v>
       </c>
@@ -11923,7 +13860,7 @@
         </is>
       </c>
       <c r="Q185" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R185" t="n">
         <v>45</v>
@@ -11984,6 +13921,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P186" t="n">
+        <v>53</v>
+      </c>
       <c r="Q186" t="b">
         <v>0</v>
       </c>
@@ -12046,8 +13996,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P187" t="n">
+        <v>51</v>
+      </c>
       <c r="Q187" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R187" t="n">
         <v>45</v>
@@ -12108,6 +14071,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P188" t="n">
+        <v>47</v>
+      </c>
       <c r="Q188" t="b">
         <v>0</v>
       </c>
@@ -12170,6 +14146,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P189" t="n">
+        <v>43</v>
+      </c>
       <c r="Q189" t="b">
         <v>0</v>
       </c>
@@ -12232,6 +14221,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P190" t="n">
+        <v>39</v>
+      </c>
       <c r="Q190" t="b">
         <v>0</v>
       </c>
@@ -12295,7 +14297,7 @@
         </is>
       </c>
       <c r="Q191" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R191" t="n">
         <v>45</v>
@@ -12356,6 +14358,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P192" t="n">
+        <v>53</v>
+      </c>
       <c r="Q192" t="b">
         <v>0</v>
       </c>
@@ -12418,6 +14433,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P193" t="n">
+        <v>70</v>
+      </c>
       <c r="Q193" t="b">
         <v>0</v>
       </c>
@@ -12480,6 +14508,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P194" t="n">
+        <v>48</v>
+      </c>
       <c r="Q194" t="b">
         <v>0</v>
       </c>
@@ -12542,6 +14583,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P195" t="n">
+        <v>58</v>
+      </c>
       <c r="Q195" t="b">
         <v>0</v>
       </c>
@@ -12604,6 +14658,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P196" t="n">
+        <v>61</v>
+      </c>
       <c r="Q196" t="b">
         <v>0</v>
       </c>
@@ -12666,6 +14733,19 @@
           <t>CPI</t>
         </is>
       </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P197" t="n">
+        <v>51</v>
+      </c>
       <c r="Q197" t="b">
         <v>0</v>
       </c>
@@ -12729,7 +14809,7 @@
         </is>
       </c>
       <c r="Q198" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R198" t="n">
         <v>45</v>
@@ -12790,6 +14870,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P199" t="n">
+        <v>67</v>
+      </c>
       <c r="Q199" t="b">
         <v>0</v>
       </c>
@@ -12852,6 +14945,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P200" t="n">
+        <v>50</v>
+      </c>
       <c r="Q200" t="b">
         <v>0</v>
       </c>
@@ -12914,6 +15020,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P201" t="n">
+        <v>62</v>
+      </c>
       <c r="Q201" t="b">
         <v>0</v>
       </c>
@@ -12976,6 +15095,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P202" t="n">
+        <v>55</v>
+      </c>
       <c r="Q202" t="b">
         <v>0</v>
       </c>
@@ -13039,7 +15171,7 @@
         </is>
       </c>
       <c r="Q203" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R203" t="n">
         <v>45</v>
@@ -13100,6 +15232,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P204" t="n">
+        <v>41</v>
+      </c>
       <c r="Q204" t="b">
         <v>0</v>
       </c>
@@ -13162,6 +15307,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P205" t="n">
+        <v>60</v>
+      </c>
       <c r="Q205" t="b">
         <v>1</v>
       </c>
@@ -13224,6 +15382,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P206" t="n">
+        <v>45</v>
+      </c>
       <c r="Q206" t="b">
         <v>0</v>
       </c>
@@ -13286,6 +15457,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P207" t="n">
+        <v>42</v>
+      </c>
       <c r="Q207" t="b">
         <v>0</v>
       </c>
@@ -13349,7 +15533,7 @@
         </is>
       </c>
       <c r="Q208" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R208" t="n">
         <v>45</v>
@@ -13410,6 +15594,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P209" t="n">
+        <v>56</v>
+      </c>
       <c r="Q209" t="b">
         <v>0</v>
       </c>
@@ -13472,6 +15669,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P210" t="n">
+        <v>47</v>
+      </c>
       <c r="Q210" t="b">
         <v>0</v>
       </c>
@@ -13534,6 +15744,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P211" t="n">
+        <v>28</v>
+      </c>
       <c r="Q211" t="b">
         <v>0</v>
       </c>
@@ -13596,6 +15819,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P212" t="n">
+        <v>42</v>
+      </c>
       <c r="Q212" t="b">
         <v>0</v>
       </c>
@@ -13659,7 +15895,7 @@
         </is>
       </c>
       <c r="Q213" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R213" t="n">
         <v>45</v>
@@ -13720,6 +15956,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P214" t="n">
+        <v>44</v>
+      </c>
       <c r="Q214" t="b">
         <v>0</v>
       </c>
@@ -13782,6 +16031,19 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P215" t="n">
+        <v>47</v>
+      </c>
       <c r="Q215" t="b">
         <v>0</v>
       </c>
@@ -13845,7 +16107,7 @@
         </is>
       </c>
       <c r="Q216" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R216" t="n">
         <v>45</v>
@@ -13906,6 +16168,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P217" t="n">
+        <v>45</v>
+      </c>
       <c r="Q217" t="b">
         <v>0</v>
       </c>
@@ -13968,6 +16243,19 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P218" t="n">
+        <v>60</v>
+      </c>
       <c r="Q218" t="b">
         <v>0</v>
       </c>
@@ -14030,6 +16318,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P219" t="n">
+        <v>62</v>
+      </c>
       <c r="Q219" t="b">
         <v>0</v>
       </c>
@@ -14092,6 +16393,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P220" t="n">
+        <v>54</v>
+      </c>
       <c r="Q220" t="b">
         <v>0</v>
       </c>
@@ -14154,6 +16468,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P221" t="n">
+        <v>56</v>
+      </c>
       <c r="Q221" t="b">
         <v>0</v>
       </c>
@@ -14217,7 +16544,7 @@
         </is>
       </c>
       <c r="Q222" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R222" t="n">
         <v>45</v>
@@ -14278,6 +16605,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P223" t="n">
+        <v>56</v>
+      </c>
       <c r="Q223" t="b">
         <v>0</v>
       </c>
@@ -14340,6 +16680,19 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P224" t="n">
+        <v>47</v>
+      </c>
       <c r="Q224" t="b">
         <v>0</v>
       </c>
@@ -14402,6 +16755,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P225" t="n">
+        <v>62</v>
+      </c>
       <c r="Q225" t="b">
         <v>0</v>
       </c>
@@ -14464,8 +16830,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P226" t="n">
+        <v>59</v>
+      </c>
       <c r="Q226" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R226" t="n">
         <v>45</v>
@@ -14526,6 +16905,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P227" t="n">
+        <v>46</v>
+      </c>
       <c r="Q227" t="b">
         <v>0</v>
       </c>
@@ -14588,6 +16980,19 @@
           <t>SHS</t>
         </is>
       </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P228" t="n">
+        <v>60</v>
+      </c>
       <c r="Q228" t="b">
         <v>0</v>
       </c>
@@ -14651,7 +17056,7 @@
         </is>
       </c>
       <c r="Q229" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R229" t="n">
         <v>45</v>
@@ -14712,6 +17117,19 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P230" t="n">
+        <v>61</v>
+      </c>
       <c r="Q230" t="b">
         <v>0</v>
       </c>
@@ -14774,6 +17192,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P231" t="n">
+        <v>48</v>
+      </c>
       <c r="Q231" t="b">
         <v>0</v>
       </c>
@@ -14836,8 +17267,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P232" t="n">
+        <v>47</v>
+      </c>
       <c r="Q232" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R232" t="n">
         <v>45</v>
@@ -14899,7 +17343,7 @@
         </is>
       </c>
       <c r="Q233" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R233" t="n">
         <v>45</v>
@@ -14960,6 +17404,19 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P234" t="n">
+        <v>58</v>
+      </c>
       <c r="Q234" t="b">
         <v>1</v>
       </c>
@@ -15022,6 +17479,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P235" t="n">
+        <v>64</v>
+      </c>
       <c r="Q235" t="b">
         <v>0</v>
       </c>
@@ -15084,6 +17554,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P236" t="n">
+        <v>56</v>
+      </c>
       <c r="Q236" t="b">
         <v>0</v>
       </c>
@@ -15146,6 +17629,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P237" t="n">
+        <v>73</v>
+      </c>
       <c r="Q237" t="b">
         <v>0</v>
       </c>
@@ -15209,7 +17705,7 @@
         </is>
       </c>
       <c r="Q238" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R238" t="n">
         <v>45</v>
@@ -15270,6 +17766,19 @@
           <t>KPA</t>
         </is>
       </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P239" t="n">
+        <v>34</v>
+      </c>
       <c r="Q239" t="b">
         <v>0</v>
       </c>
@@ -15332,8 +17841,21 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P240" t="n">
+        <v>46</v>
+      </c>
       <c r="Q240" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R240" t="n">
         <v>45</v>
@@ -15394,6 +17916,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P241" t="n">
+        <v>81</v>
+      </c>
       <c r="Q241" t="b">
         <v>0</v>
       </c>
@@ -15456,6 +17991,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P242" t="n">
+        <v>59</v>
+      </c>
       <c r="Q242" t="b">
         <v>0</v>
       </c>
@@ -15518,6 +18066,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P243" t="n">
+        <v>59</v>
+      </c>
       <c r="Q243" t="b">
         <v>0</v>
       </c>
@@ -15580,6 +18141,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P244" t="n">
+        <v>50</v>
+      </c>
       <c r="Q244" t="b">
         <v>0</v>
       </c>
@@ -15642,6 +18216,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P245" t="n">
+        <v>46</v>
+      </c>
       <c r="Q245" t="b">
         <v>0</v>
       </c>
@@ -15704,6 +18291,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P246" t="n">
+        <v>62</v>
+      </c>
       <c r="Q246" t="b">
         <v>0</v>
       </c>
@@ -15767,7 +18367,7 @@
         </is>
       </c>
       <c r="Q247" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R247" t="n">
         <v>45</v>
@@ -15828,6 +18428,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P248" t="n">
+        <v>39</v>
+      </c>
       <c r="Q248" t="b">
         <v>0</v>
       </c>
@@ -15890,6 +18503,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P249" t="n">
+        <v>56</v>
+      </c>
       <c r="Q249" t="b">
         <v>0</v>
       </c>
@@ -15952,6 +18578,19 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P250" t="n">
+        <v>52</v>
+      </c>
       <c r="Q250" t="b">
         <v>0</v>
       </c>
@@ -16014,8 +18653,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P251" t="n">
+        <v>60</v>
+      </c>
       <c r="Q251" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R251" t="n">
         <v>45</v>
@@ -16076,8 +18728,21 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P252" t="n">
+        <v>46</v>
+      </c>
       <c r="Q252" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R252" t="n">
         <v>45</v>
@@ -16139,7 +18804,7 @@
         </is>
       </c>
       <c r="Q253" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R253" t="n">
         <v>45</v>
@@ -16200,6 +18865,19 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P254" t="n">
+        <v>55</v>
+      </c>
       <c r="Q254" t="b">
         <v>1</v>
       </c>
@@ -16262,6 +18940,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P255" t="n">
+        <v>59</v>
+      </c>
       <c r="Q255" t="b">
         <v>0</v>
       </c>
@@ -16324,6 +19015,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P256" t="n">
+        <v>38</v>
+      </c>
       <c r="Q256" t="b">
         <v>0</v>
       </c>
@@ -16387,7 +19091,7 @@
         </is>
       </c>
       <c r="Q257" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R257" t="n">
         <v>45</v>
@@ -16448,6 +19152,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P258" t="n">
+        <v>56</v>
+      </c>
       <c r="Q258" t="b">
         <v>1</v>
       </c>
@@ -16510,6 +19227,19 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P259" t="n">
+        <v>58</v>
+      </c>
       <c r="Q259" t="b">
         <v>0</v>
       </c>
@@ -16572,6 +19302,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P260" t="n">
+        <v>45</v>
+      </c>
       <c r="Q260" t="b">
         <v>0</v>
       </c>
@@ -16634,6 +19377,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P261" t="n">
+        <v>69</v>
+      </c>
       <c r="Q261" t="b">
         <v>0</v>
       </c>
@@ -16697,7 +19453,7 @@
         </is>
       </c>
       <c r="Q262" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R262" t="n">
         <v>45</v>
@@ -16758,6 +19514,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P263" t="n">
+        <v>56</v>
+      </c>
       <c r="Q263" t="b">
         <v>1</v>
       </c>
@@ -16820,6 +19589,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P264" t="n">
+        <v>39</v>
+      </c>
       <c r="Q264" t="b">
         <v>0</v>
       </c>
@@ -16882,6 +19664,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P265" t="n">
+        <v>77</v>
+      </c>
       <c r="Q265" t="b">
         <v>0</v>
       </c>
@@ -16945,7 +19740,7 @@
         </is>
       </c>
       <c r="Q266" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R266" t="n">
         <v>45</v>
@@ -17006,6 +19801,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P267" t="n">
+        <v>67</v>
+      </c>
       <c r="Q267" t="b">
         <v>0</v>
       </c>
@@ -17068,6 +19876,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P268" t="n">
+        <v>69</v>
+      </c>
       <c r="Q268" t="b">
         <v>0</v>
       </c>
@@ -17130,6 +19951,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P269" t="n">
+        <v>39</v>
+      </c>
       <c r="Q269" t="b">
         <v>0</v>
       </c>
@@ -17192,6 +20026,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P270" t="n">
+        <v>59</v>
+      </c>
       <c r="Q270" t="b">
         <v>0</v>
       </c>
@@ -17254,6 +20101,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P271" t="n">
+        <v>60</v>
+      </c>
       <c r="Q271" t="b">
         <v>0</v>
       </c>
@@ -17316,6 +20176,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P272" t="n">
+        <v>42</v>
+      </c>
       <c r="Q272" t="b">
         <v>0</v>
       </c>
@@ -17379,7 +20252,7 @@
         </is>
       </c>
       <c r="Q273" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R273" t="n">
         <v>45</v>
@@ -17440,6 +20313,19 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P274" t="n">
+        <v>54</v>
+      </c>
       <c r="Q274" t="b">
         <v>1</v>
       </c>
@@ -17502,6 +20388,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P275" t="n">
+        <v>55</v>
+      </c>
       <c r="Q275" t="b">
         <v>0</v>
       </c>
@@ -17564,6 +20463,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P276" t="n">
+        <v>43</v>
+      </c>
       <c r="Q276" t="b">
         <v>0</v>
       </c>
@@ -17626,6 +20538,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P277" t="n">
+        <v>48</v>
+      </c>
       <c r="Q277" t="b">
         <v>0</v>
       </c>
@@ -17689,7 +20614,7 @@
         </is>
       </c>
       <c r="Q278" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R278" t="n">
         <v>45</v>
@@ -17750,6 +20675,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P279" t="n">
+        <v>45</v>
+      </c>
       <c r="Q279" t="b">
         <v>0</v>
       </c>
@@ -17812,6 +20750,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P280" t="n">
+        <v>63</v>
+      </c>
       <c r="Q280" t="b">
         <v>0</v>
       </c>
@@ -17874,6 +20825,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P281" t="n">
+        <v>62</v>
+      </c>
       <c r="Q281" t="b">
         <v>0</v>
       </c>
@@ -17936,6 +20900,19 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P282" t="n">
+        <v>60</v>
+      </c>
       <c r="Q282" t="b">
         <v>0</v>
       </c>
@@ -17999,7 +20976,7 @@
         </is>
       </c>
       <c r="Q283" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R283" t="n">
         <v>45</v>
@@ -18060,6 +21037,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P284" t="n">
+        <v>43</v>
+      </c>
       <c r="Q284" t="b">
         <v>0</v>
       </c>
@@ -18122,6 +21112,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P285" t="n">
+        <v>71</v>
+      </c>
       <c r="Q285" t="b">
         <v>1</v>
       </c>
@@ -18185,7 +21188,7 @@
         </is>
       </c>
       <c r="Q286" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R286" t="n">
         <v>45</v>
@@ -18246,6 +21249,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P287" t="n">
+        <v>47</v>
+      </c>
       <c r="Q287" t="b">
         <v>0</v>
       </c>
@@ -18308,6 +21324,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P288" t="n">
+        <v>66</v>
+      </c>
       <c r="Q288" t="b">
         <v>0</v>
       </c>
@@ -18370,6 +21399,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P289" t="n">
+        <v>64</v>
+      </c>
       <c r="Q289" t="b">
         <v>0</v>
       </c>
@@ -18433,7 +21475,7 @@
         </is>
       </c>
       <c r="Q290" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R290" t="n">
         <v>45</v>
@@ -18494,6 +21536,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P291" t="n">
+        <v>57</v>
+      </c>
       <c r="Q291" t="b">
         <v>1</v>
       </c>
@@ -18556,6 +21611,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P292" t="n">
+        <v>53</v>
+      </c>
       <c r="Q292" t="b">
         <v>0</v>
       </c>
@@ -18618,6 +21686,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P293" t="n">
+        <v>45</v>
+      </c>
       <c r="Q293" t="b">
         <v>0</v>
       </c>
@@ -18680,6 +21761,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P294" t="n">
+        <v>60</v>
+      </c>
       <c r="Q294" t="b">
         <v>0</v>
       </c>
@@ -18742,6 +21836,19 @@
           <t>SHS</t>
         </is>
       </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P295" t="n">
+        <v>39</v>
+      </c>
       <c r="Q295" t="b">
         <v>0</v>
       </c>
@@ -18804,6 +21911,19 @@
           <t>LJPRV</t>
         </is>
       </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P296" t="n">
+        <v>66</v>
+      </c>
       <c r="Q296" t="b">
         <v>0</v>
       </c>
@@ -18867,7 +21987,7 @@
         </is>
       </c>
       <c r="Q297" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R297" t="n">
         <v>45</v>
@@ -18928,6 +22048,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P298" t="n">
+        <v>47</v>
+      </c>
       <c r="Q298" t="b">
         <v>0</v>
       </c>
@@ -18990,8 +22123,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P299" t="n">
+        <v>64</v>
+      </c>
       <c r="Q299" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R299" t="n">
         <v>45</v>
@@ -19052,6 +22198,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P300" t="n">
+        <v>47</v>
+      </c>
       <c r="Q300" t="b">
         <v>0</v>
       </c>
@@ -19114,6 +22273,19 @@
           <t>SHS</t>
         </is>
       </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P301" t="n">
+        <v>67</v>
+      </c>
       <c r="Q301" t="b">
         <v>0</v>
       </c>
@@ -19176,6 +22348,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P302" t="n">
+        <v>58</v>
+      </c>
       <c r="Q302" t="b">
         <v>0</v>
       </c>
@@ -19238,6 +22423,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P303" t="n">
+        <v>64</v>
+      </c>
       <c r="Q303" t="b">
         <v>0</v>
       </c>
@@ -19301,7 +22499,7 @@
         </is>
       </c>
       <c r="Q304" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R304" t="n">
         <v>45</v>
@@ -19362,6 +22560,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P305" t="n">
+        <v>60</v>
+      </c>
       <c r="Q305" t="b">
         <v>0</v>
       </c>
@@ -19424,8 +22635,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P306" t="n">
+        <v>60</v>
+      </c>
       <c r="Q306" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R306" t="n">
         <v>45</v>
@@ -19486,6 +22710,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P307" t="n">
+        <v>56</v>
+      </c>
       <c r="Q307" t="b">
         <v>0</v>
       </c>
@@ -19548,6 +22785,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P308" t="n">
+        <v>48</v>
+      </c>
       <c r="Q308" t="b">
         <v>0</v>
       </c>
@@ -19610,6 +22860,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P309" t="n">
+        <v>53</v>
+      </c>
       <c r="Q309" t="b">
         <v>0</v>
       </c>
@@ -19672,6 +22935,19 @@
           <t>KNA</t>
         </is>
       </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P310" t="n">
+        <v>74</v>
+      </c>
       <c r="Q310" t="b">
         <v>0</v>
       </c>
@@ -19735,7 +23011,7 @@
         </is>
       </c>
       <c r="Q311" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R311" t="n">
         <v>45</v>
@@ -19796,6 +23072,19 @@
           <t>LJPRV</t>
         </is>
       </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P312" t="n">
+        <v>60</v>
+      </c>
       <c r="Q312" t="b">
         <v>0</v>
       </c>
@@ -19858,6 +23147,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P313" t="n">
+        <v>47</v>
+      </c>
       <c r="Q313" t="b">
         <v>0</v>
       </c>
@@ -19920,6 +23222,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P314" t="n">
+        <v>64</v>
+      </c>
       <c r="Q314" t="b">
         <v>0</v>
       </c>
@@ -19982,8 +23297,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P315" t="n">
+        <v>71</v>
+      </c>
       <c r="Q315" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R315" t="n">
         <v>45</v>
@@ -20044,6 +23372,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P316" t="n">
+        <v>42</v>
+      </c>
       <c r="Q316" t="b">
         <v>0</v>
       </c>
@@ -20106,6 +23447,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P317" t="n">
+        <v>41</v>
+      </c>
       <c r="Q317" t="b">
         <v>0</v>
       </c>
@@ -20168,6 +23522,19 @@
           <t>KNA</t>
         </is>
       </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P318" t="n">
+        <v>43</v>
+      </c>
       <c r="Q318" t="b">
         <v>0</v>
       </c>
@@ -20230,6 +23597,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P319" t="n">
+        <v>52</v>
+      </c>
       <c r="Q319" t="b">
         <v>0</v>
       </c>
@@ -20293,7 +23673,7 @@
         </is>
       </c>
       <c r="Q320" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R320" t="n">
         <v>45</v>
@@ -20354,6 +23734,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P321" t="n">
+        <v>51</v>
+      </c>
       <c r="Q321" t="b">
         <v>0</v>
       </c>
@@ -20416,6 +23809,19 @@
           <t>KPA</t>
         </is>
       </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P322" t="n">
+        <v>46</v>
+      </c>
       <c r="Q322" t="b">
         <v>0</v>
       </c>
@@ -20478,6 +23884,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P323" t="n">
+        <v>62</v>
+      </c>
       <c r="Q323" t="b">
         <v>0</v>
       </c>
@@ -20540,6 +23959,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P324" t="n">
+        <v>58</v>
+      </c>
       <c r="Q324" t="b">
         <v>0</v>
       </c>
@@ -20602,6 +24034,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P325" t="n">
+        <v>61</v>
+      </c>
       <c r="Q325" t="b">
         <v>0</v>
       </c>
@@ -20665,7 +24110,7 @@
         </is>
       </c>
       <c r="Q326" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R326" t="n">
         <v>45</v>
